--- a/produtos_ua.xlsx
+++ b/produtos_ua.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3FF5BF-2164-4227-A5AD-625DCC994D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA753BF-C819-497A-B8C0-47CFA2D1C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="122">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -149,9 +149,6 @@
     <t>Corrida</t>
   </si>
   <si>
-    <t>6014730</t>
-  </si>
-  <si>
     <t>UA CHARGED NONSTOP</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>BKBKTX</t>
   </si>
   <si>
-    <t>6014732</t>
-  </si>
-  <si>
     <t>UA CHARGED ENDLESS</t>
   </si>
   <si>
@@ -203,9 +197,6 @@
     <t>Feminino</t>
   </si>
   <si>
-    <t>6014736</t>
-  </si>
-  <si>
     <t>UA CHARGED SKYLINE 5</t>
   </si>
   <si>
@@ -221,9 +212,6 @@
     <t>SGBKSG</t>
   </si>
   <si>
-    <t>6006985</t>
-  </si>
-  <si>
     <t>UA CHARGED QUICKER 2</t>
   </si>
   <si>
@@ -248,9 +236,6 @@
     <t>MGRAYB</t>
   </si>
   <si>
-    <t>6020667</t>
-  </si>
-  <si>
     <t>UA CHARGED SLIGHT 4</t>
   </si>
   <si>
@@ -266,9 +251,6 @@
     <t>BKMPMP</t>
   </si>
   <si>
-    <t>6014744</t>
-  </si>
-  <si>
     <t>UA CHARGED SUNNY</t>
   </si>
   <si>
@@ -287,9 +269,6 @@
     <t>APAPPP</t>
   </si>
   <si>
-    <t>6020665</t>
-  </si>
-  <si>
     <t>UA CHARGED WING 2 SE</t>
   </si>
   <si>
@@ -305,9 +284,6 @@
     <t>Treino</t>
   </si>
   <si>
-    <t>6014745</t>
-  </si>
-  <si>
     <t>UA TRIBASE CROSS 2 SE</t>
   </si>
   <si>
@@ -320,9 +296,6 @@
     <t>BKCABK</t>
   </si>
   <si>
-    <t>6020660</t>
-  </si>
-  <si>
     <t>UA TRIBASE REPS 3</t>
   </si>
   <si>
@@ -347,9 +320,6 @@
     <t>BASQUETE</t>
   </si>
   <si>
-    <t>6014748</t>
-  </si>
-  <si>
     <t>UA LAYUP</t>
   </si>
   <si>
@@ -365,9 +335,6 @@
     <t>BKCAWH</t>
   </si>
   <si>
-    <t>6020662</t>
-  </si>
-  <si>
     <t>UA BALLER</t>
   </si>
   <si>
@@ -383,9 +350,6 @@
     <t>Chinelos</t>
   </si>
   <si>
-    <t>3025902</t>
-  </si>
-  <si>
     <t>UA IGNITE VI SL</t>
   </si>
   <si>
@@ -398,18 +362,12 @@
     <t>WHWHBA</t>
   </si>
   <si>
-    <t>3027787</t>
-  </si>
-  <si>
     <t>UA CORE 2</t>
   </si>
   <si>
     <t>WTWTBK</t>
   </si>
   <si>
-    <t>6006999</t>
-  </si>
-  <si>
     <t>UA ANSA LIGHT</t>
   </si>
   <si>
@@ -419,9 +377,6 @@
     <t>WTBKBK</t>
   </si>
   <si>
-    <t>6020663</t>
-  </si>
-  <si>
     <t>UA CHARGED FLEEK</t>
   </si>
   <si>
@@ -440,13 +395,13 @@
     <t>BKMTSC</t>
   </si>
   <si>
-    <t>3027786</t>
-  </si>
-  <si>
     <t>UA DAILY</t>
   </si>
   <si>
     <t>NÃO</t>
+  </si>
+  <si>
+    <t>CHI</t>
   </si>
 </sst>
 </file>
@@ -467,6 +422,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -480,6 +436,7 @@
       <sz val="11"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -578,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,6 +564,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,12 +870,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -934,7 +894,7 @@
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
@@ -1042,54 +1002,54 @@
         <f t="shared" ref="A2:A33" si="0">CONCATENATE(D2,"_",G2)</f>
         <v>6014730_BFDGFL</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3">
         <v>599.99</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
@@ -1097,54 +1057,54 @@
         <f t="shared" si="0"/>
         <v>6014730_SWSWEB</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="3">
         <v>599.99</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R3" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
@@ -1152,54 +1112,54 @@
         <f t="shared" si="0"/>
         <v>6014730_BKBKMP</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="3">
         <v>599.99</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R4" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
@@ -1207,26 +1167,26 @@
         <f t="shared" si="0"/>
         <v>6014730_BKBKTX</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="3">
         <v>599.99</v>
@@ -1234,25 +1194,25 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R5" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
@@ -1260,54 +1220,54 @@
         <f t="shared" si="0"/>
         <v>6014732_SADTEB</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="1">
+        <v>6014732</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I6" s="3">
         <v>499.99</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R6" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
@@ -1315,54 +1275,54 @@
         <f t="shared" si="0"/>
         <v>6014732_CABKBO</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>47</v>
+      <c r="D7" s="1">
+        <v>6014732</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I7" s="3">
         <v>499.99</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R7" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
@@ -1370,26 +1330,26 @@
         <f t="shared" si="0"/>
         <v>6014732_BKCAMP</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>47</v>
+      <c r="D8" s="1">
+        <v>6014732</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I8" s="3">
         <v>499.99</v>
@@ -1397,25 +1357,25 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R8" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
@@ -1423,54 +1383,54 @@
         <f t="shared" si="0"/>
         <v>6014732_BFDGFL</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
+      <c r="D9" s="1">
+        <v>6014732</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="3">
         <v>499.99</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q9" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R9" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
@@ -1478,54 +1438,54 @@
         <f t="shared" si="0"/>
         <v>6014732_WHPEPK</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>47</v>
+      <c r="D10" s="1">
+        <v>6014732</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I10" s="3">
         <v>499.99</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R10" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
@@ -1533,26 +1493,26 @@
         <f t="shared" si="0"/>
         <v>6014736_BKBKCR</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>55</v>
+      <c r="D11" s="1">
+        <v>6014736</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="3">
         <v>499.99</v>
@@ -1560,25 +1520,25 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R11" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
@@ -1586,26 +1546,26 @@
         <f t="shared" si="0"/>
         <v>6014736_RYRYWH</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="1">
+        <v>6014736</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I12" s="3">
         <v>499.99</v>
@@ -1613,25 +1573,25 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R12" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
@@ -1639,26 +1599,26 @@
         <f t="shared" si="0"/>
         <v>6014736_STSTWH</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>55</v>
+      <c r="D13" s="1">
+        <v>6014736</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" s="3">
         <v>499.99</v>
@@ -1666,25 +1626,25 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R13" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
@@ -1692,54 +1652,54 @@
         <f t="shared" si="0"/>
         <v>6014736_SGBKSG</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
+      <c r="D14" s="1">
+        <v>6014736</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I14" s="3">
         <v>499.99</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R14" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
@@ -1747,26 +1707,26 @@
         <f t="shared" si="0"/>
         <v>6006985_CACAMG</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>61</v>
+      <c r="D15" s="1">
+        <v>6006985</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I15" s="3">
         <v>499.99</v>
@@ -1774,25 +1734,25 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q15" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R15" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
@@ -1800,26 +1760,26 @@
         <f t="shared" si="0"/>
         <v>6006985_CABKMS</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>61</v>
+      <c r="D16" s="1">
+        <v>6006985</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I16" s="3">
         <v>499.99</v>
@@ -1827,25 +1787,25 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R16" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1853,26 +1813,26 @@
         <f t="shared" si="0"/>
         <v>6006985_FOFOBR</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I17" s="3">
         <v>499.99</v>
@@ -1880,25 +1840,25 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1906,54 +1866,54 @@
         <f t="shared" si="0"/>
         <v>6006985_CRCRMP</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>61</v>
+      <c r="D18" s="1">
+        <v>6006985</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I18" s="3">
         <v>499.99</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R18" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1961,26 +1921,26 @@
         <f t="shared" si="0"/>
         <v>6006985_MGMGBK</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>61</v>
+      <c r="D19" s="1">
+        <v>6006985</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I19" s="3">
         <v>499.99</v>
@@ -1988,25 +1948,25 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q19" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R19" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2014,26 +1974,26 @@
         <f t="shared" si="0"/>
         <v>6006985_SWSWTU</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>61</v>
+      <c r="D20" s="1">
+        <v>6006985</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I20" s="3">
         <v>499.99</v>
@@ -2041,25 +2001,25 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q20" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R20" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2067,356 +2027,356 @@
         <f t="shared" si="0"/>
         <v>6006985_MGRAYB</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
+      <c r="D21" s="1">
+        <v>6006985</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I21" s="3">
         <v>499.99</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q21" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>6020667_ACBKDG</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>70</v>
+      <c r="D22" s="1">
+        <v>6020667</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I22" s="3">
         <v>399.99</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>6020667_TITIBK</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>70</v>
+      <c r="D23" s="1">
+        <v>6020667</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I23" s="3">
         <v>399.99</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>6020667_SWCKEB</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
+      <c r="D24" s="1">
+        <v>6020667</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I24" s="3">
         <v>399.99</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>6020667_BKMPMP</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="1">
+        <v>6020667</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I25" s="3">
         <v>399.99</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>6020667_BKCAMP</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>70</v>
+      <c r="D26" s="1">
+        <v>6020667</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I26" s="3">
         <v>399.99</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>6014744_BKBKMP</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>76</v>
+      <c r="D27" s="1">
+        <v>6014744</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I27" s="3">
         <v>379.99</v>
@@ -2424,52 +2384,52 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>6014744_SGSGBK</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>76</v>
+      <c r="D28" s="1">
+        <v>6014744</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I28" s="3">
         <v>379.99</v>
@@ -2477,52 +2437,52 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>6014744_AGAGWH</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C29" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>76</v>
+      <c r="D29" s="1">
+        <v>6014744</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I29" s="3">
         <v>379.99</v>
@@ -2530,465 +2490,465 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>6014744_BNBKMP</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>76</v>
+      <c r="D30" s="1">
+        <v>6014744</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I30" s="3">
         <v>379.99</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>6014744_CASBMG</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>76</v>
+      <c r="D31" s="1">
+        <v>6014744</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I31" s="3">
         <v>379.99</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>6014744_APAPPP</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I32" s="3">
         <v>379.99</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>6020665_BKBKMP</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>83</v>
+      <c r="D33" s="1">
+        <v>6020665</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I33" s="3">
         <v>359.99</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" ref="A34:A66" si="1">CONCATENATE(D34,"_",G34)</f>
         <v>6020665_CRCRMP</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>83</v>
+      <c r="D34" s="1">
+        <v>6020665</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I34" s="3">
         <v>359.99</v>
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R34" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="1"/>
         <v>6020665_MGMOMP</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>83</v>
+      <c r="D35" s="1">
+        <v>6020665</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I35" s="3">
         <v>359.99</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="1"/>
         <v>6020665_ACACMP</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C36" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>83</v>
+      <c r="D36" s="1">
+        <v>6020665</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I36" s="3">
         <v>359.99</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="1"/>
         <v>6020665_SWSWCK</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C37" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>83</v>
+      <c r="D37" s="1">
+        <v>6020665</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I37" s="3">
         <v>359.99</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -2996,26 +2956,26 @@
         <f t="shared" si="1"/>
         <v>6014745_CRFGVR</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
+      </c>
+      <c r="D38" s="1">
+        <v>6014745</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I38" s="3">
         <v>599.99</v>
@@ -3023,25 +2983,25 @@
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="L38" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P38" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="Q38" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R38" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -3049,26 +3009,26 @@
         <f t="shared" si="1"/>
         <v>6014745_FGLLPP</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
+      </c>
+      <c r="D39" s="1">
+        <v>6014745</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I39" s="3">
         <v>599.99</v>
@@ -3076,25 +3036,25 @@
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="L39" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P39" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="Q39" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R39" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -3102,54 +3062,54 @@
         <f t="shared" si="1"/>
         <v>6014745_BKCABK</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
+      </c>
+      <c r="D40" s="1">
+        <v>6014745</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I40" s="3">
         <v>599.99</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P40" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="Q40" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R40" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -3157,54 +3117,54 @@
         <f t="shared" si="1"/>
         <v>6020660_MOGBGC</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
+      </c>
+      <c r="D41" s="1">
+        <v>6020660</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I41" s="3">
         <v>549.99</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q41" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R41" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -3212,54 +3172,54 @@
         <f t="shared" si="1"/>
         <v>6020660_VVVVLC</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I42" s="3">
         <v>549.99</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q42" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R42" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -3267,54 +3227,54 @@
         <f t="shared" si="1"/>
         <v>6020660_SWSWPP</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
+      </c>
+      <c r="D43" s="1">
+        <v>6020660</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I43" s="3">
         <v>549.99</v>
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q43" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R43" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -3322,54 +3282,54 @@
         <f t="shared" si="1"/>
         <v>6020660_BKRRSA</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
+      </c>
+      <c r="D44" s="1">
+        <v>6020660</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I44" s="3">
         <v>549.99</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q44" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R44" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -3377,54 +3337,54 @@
         <f t="shared" si="1"/>
         <v>6020660_SWSWBN</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
+      </c>
+      <c r="D45" s="1">
+        <v>6020660</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I45" s="3">
         <v>549.99</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q45" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R45" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -3432,136 +3392,136 @@
         <f t="shared" si="1"/>
         <v>6020660_BLKBKW</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6020660</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I46" s="3">
         <v>549.99</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q46" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R46" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="1"/>
         <v>6014748_MPPCTX</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
+      </c>
+      <c r="D47" s="1">
+        <v>6014748</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I47" s="3">
         <v>549.99</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R47" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="1"/>
         <v>6014748_WMTGBK</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
+      </c>
+      <c r="D48" s="1">
+        <v>6014748</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I48" s="3">
         <v>549.99</v>
@@ -3569,80 +3529,80 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
       <c r="L48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R48" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="1"/>
         <v>6014748_BKCAWH</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6014748</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I49" s="3">
         <v>549.99</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -3650,54 +3610,54 @@
         <f t="shared" si="1"/>
         <v>6020662_BKGMPU</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
+      </c>
+      <c r="D50" s="1">
+        <v>6020662</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I50" s="3">
         <v>499.99</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q50" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R50" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -3705,54 +3665,54 @@
         <f t="shared" si="1"/>
         <v>6020662_BKWHPU</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
+      </c>
+      <c r="D51" s="1">
+        <v>6020662</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I51" s="3">
         <v>499.99</v>
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q51" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R51" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -3760,81 +3720,81 @@
         <f t="shared" si="1"/>
         <v>6020662_WHMGWT</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C52" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="1">
+        <v>6020662</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="H52" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I52" s="3">
         <v>499.99</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q52" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R52" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f t="shared" si="1"/>
         <v>3025902_BKBKWT</v>
       </c>
-      <c r="B53" t="s">
-        <v>3</v>
+      <c r="B53" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3025902</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I53" s="3">
         <v>229.99</v>
@@ -3842,52 +3802,52 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R53" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f t="shared" si="1"/>
         <v>3025902_WHWHBA</v>
       </c>
-      <c r="B54" t="s">
-        <v>3</v>
+      <c r="B54" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3025902</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I54" s="3">
         <v>229.99</v>
@@ -3895,52 +3855,52 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
       <c r="L54" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R54" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f t="shared" si="1"/>
         <v>3027787_WTWTBK</v>
       </c>
-      <c r="B55" t="s">
-        <v>3</v>
+      <c r="B55" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
+      </c>
+      <c r="D55" s="1">
+        <v>3027787</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I55" s="3">
         <v>139.99</v>
@@ -3948,52 +3908,52 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
       <c r="L55" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f t="shared" si="1"/>
         <v>3027787_BLKBKW</v>
       </c>
-      <c r="B56" t="s">
-        <v>3</v>
+      <c r="B56" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3027787</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I56" s="3">
         <v>139.99</v>
@@ -4001,52 +3961,52 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R56" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f t="shared" si="1"/>
         <v>6006999_MNYDWG</v>
       </c>
-      <c r="B57" t="s">
-        <v>3</v>
+      <c r="B57" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
+      </c>
+      <c r="D57" s="1">
+        <v>6006999</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I57" s="3">
         <v>129.99</v>
@@ -4054,52 +4014,52 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
       <c r="L57" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R57" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f t="shared" si="1"/>
         <v>6006999_WTBKBK</v>
       </c>
-      <c r="B58" t="s">
-        <v>3</v>
+      <c r="B58" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
+      </c>
+      <c r="D58" s="1">
+        <v>6006999</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I58" s="3">
         <v>129.99</v>
@@ -4107,52 +4067,52 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R58" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f t="shared" si="1"/>
         <v>6006999_BLKBKW</v>
       </c>
-      <c r="B59" t="s">
-        <v>3</v>
+      <c r="B59" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
+      </c>
+      <c r="D59" s="1">
+        <v>6006999</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I59" s="3">
         <v>129.99</v>
@@ -4160,327 +4120,327 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
       <c r="L59" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R59" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="1"/>
         <v>6020663_WHPPPE</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C60" t="s">
         <v>36</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>127</v>
+      <c r="D60" s="1">
+        <v>6020663</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I60" s="3">
         <v>399.99</v>
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M60" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R60" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="1"/>
         <v>6020663_BFBFBF</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>127</v>
+      <c r="D61" s="1">
+        <v>6020663</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I61" s="3">
         <v>399.99</v>
       </c>
       <c r="J61" s="4"/>
       <c r="K61" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L61" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M61" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R61" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="1"/>
         <v>6020663_TITIPP</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>127</v>
+      <c r="D62" s="1">
+        <v>6020663</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I62" s="3">
         <v>399.99</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M62" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R62" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="1"/>
         <v>6020663_SARPBR</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C63" t="s">
         <v>36</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>127</v>
+      <c r="D63" s="1">
+        <v>6020663</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I63" s="3">
         <v>399.99</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L63" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M63" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R63" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="1"/>
         <v>6020663_BKMTSC</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C64" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>127</v>
+      <c r="D64" s="1">
+        <v>6020663</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I64" s="3">
         <v>399.99</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M64" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R64" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f t="shared" si="1"/>
         <v>3027786_BLKBKW</v>
       </c>
-      <c r="B65" t="s">
-        <v>3</v>
+      <c r="B65" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C65" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>134</v>
+        <v>103</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3027786</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I65" s="3">
         <v>149.99</v>
@@ -4488,52 +4448,52 @@
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
       <c r="L65" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R65" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f t="shared" si="1"/>
         <v>3027786_WTWTBK</v>
       </c>
-      <c r="B66" t="s">
-        <v>3</v>
+      <c r="B66" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>134</v>
+        <v>103</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3027786</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I66" s="3">
         <v>149.99</v>
@@ -4541,33 +4501,29 @@
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
       <c r="L66" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI66" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="17">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AI66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>